--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1632.336</v>
+        <v>73379.10000000001</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>165.647</v>
+        <v>7446.4</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1448.04</v>
+        <v>65094.36</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>329.1</v>
+        <v>14794.17</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1566.516</v>
+        <v>70420.27</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>27.93</v>
+        <v>1255.55</v>
       </c>
     </row>
     <row r="8">
@@ -935,11 +935,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>244.412</v>
+        <v>10987.16</v>
       </c>
     </row>
     <row r="9">
@@ -996,11 +996,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>38.395</v>
+        <v>1725.99</v>
       </c>
     </row>
     <row r="10">
@@ -1057,11 +1057,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>131.64</v>
+        <v>5917.67</v>
       </c>
     </row>
     <row r="11">
@@ -1118,11 +1118,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1557.552</v>
+        <v>70017.3</v>
       </c>
     </row>
     <row r="12">
@@ -1179,11 +1179,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1039.956</v>
+        <v>46749.59</v>
       </c>
     </row>
     <row r="13">
@@ -1240,11 +1240,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>176.617</v>
+        <v>7939.54</v>
       </c>
     </row>
     <row r="14">
@@ -1301,11 +1301,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1487.532</v>
+        <v>66869.66</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>495.9</v>
+        <v>22292.41</v>
       </c>
     </row>
     <row r="16">
@@ -1423,11 +1423,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1145.268</v>
+        <v>51483.72</v>
       </c>
     </row>
     <row r="17">
@@ -1484,11 +1484,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1619.172</v>
+        <v>72787.33</v>
       </c>
     </row>
     <row r="18">
@@ -1545,11 +1545,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>988.722</v>
+        <v>44446.44</v>
       </c>
     </row>
     <row r="19">
@@ -1610,11 +1610,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1138.686</v>
+        <v>51187.84</v>
       </c>
     </row>
     <row r="20">
@@ -1671,11 +1671,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1480.95</v>
+        <v>66573.78</v>
       </c>
     </row>
     <row r="21">
@@ -1732,11 +1732,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1606.008</v>
+        <v>72195.57000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1793,11 +1793,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>242.437</v>
+        <v>10898.37</v>
       </c>
     </row>
     <row r="23">
@@ -1854,11 +1854,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>895.152</v>
+        <v>40240.15</v>
       </c>
     </row>
     <row r="24">
@@ -1915,11 +1915,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>231.467</v>
+        <v>10405.24</v>
       </c>
     </row>
     <row r="25">
@@ -1976,11 +1976,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1137.864</v>
+        <v>51150.89</v>
       </c>
     </row>
     <row r="26">
@@ -2037,11 +2037,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>209.527</v>
+        <v>9418.959999999999</v>
       </c>
     </row>
     <row r="27">
@@ -2098,11 +2098,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>208.43</v>
+        <v>9369.639999999999</v>
       </c>
     </row>
     <row r="28">
@@ -2159,11 +2159,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>102.021</v>
+        <v>4586.19</v>
       </c>
     </row>
     <row r="29">
@@ -2220,11 +2220,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1724.484</v>
+        <v>77521.47</v>
       </c>
     </row>
     <row r="30">
@@ -2281,11 +2281,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>819.4589999999999</v>
+        <v>36837.49</v>
       </c>
     </row>
     <row r="31">
@@ -2342,11 +2342,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>156.871</v>
+        <v>7051.89</v>
       </c>
     </row>
     <row r="32">
@@ -2403,11 +2403,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1341.631</v>
+        <v>60310.91</v>
       </c>
     </row>
     <row r="33">
@@ -2464,11 +2464,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>155.774</v>
+        <v>7002.58</v>
       </c>
     </row>
   </sheetData>
